--- a/data/Ascona/investment_decision/Ascona_district_investment_decision.xlsx
+++ b/data/Ascona/investment_decision/Ascona_district_investment_decision.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,52 +440,52 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>scen_all_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>scale_MW</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>scen_all_candidate_unit</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>scen_base_invested_available_unit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>scale_MW</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>scen_base_candidate_unit</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_candidate_unit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -505,25 +505,25 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>38.83232050396268</v>
+        <v>12.02681808690701</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>38.83232050396268</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>11.85896762513558</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>11.85896762513558</v>
+        <v>12.02681808690701</v>
       </c>
     </row>
     <row r="3">
@@ -542,25 +542,25 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>38.83232050396268</v>
+        <v>16.55360533516066</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>38.83232050396268</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>16.32257745401947</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>16.32257745401947</v>
+        <v>16.55360533516066</v>
       </c>
     </row>
     <row r="4">
@@ -579,25 +579,25 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>38.83232050396268</v>
+        <v>18.8204631381465</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>38.83232050396268</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>18.55779820003381</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>18.55779820003381</v>
+        <v>18.8204631381465</v>
       </c>
     </row>
     <row r="5">
@@ -616,25 +616,25 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>38.83232050396268</v>
+        <v>20.15059880314304</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>38.83232050396268</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>19.86937002844656</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>19.86937002844656</v>
+        <v>20.15059880314304</v>
       </c>
     </row>
     <row r="6">
@@ -653,25 +653,25 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>38.83232050396268</v>
+        <v>21.01808582652089</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>38.83232050396268</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>20.72475010080856</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>20.72475010080856</v>
+        <v>21.01808582652089</v>
       </c>
     </row>
     <row r="7">
@@ -679,7 +679,7 @@
         <v>46023</v>
       </c>
       <c r="B7" t="n">
-        <v>1.668885927770414</v>
+        <v>1.744576111630544</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -690,25 +690,25 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>38.83232050396268</v>
+        <v>12.02681808690701</v>
       </c>
       <c r="F7" t="n">
-        <v>1.668885927770414</v>
+        <v>1.744576111630546</v>
       </c>
       <c r="G7" t="n">
-        <v>38.83232050396268</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="H7" t="n">
-        <v>1.668885927770413</v>
+        <v>1.744576111630544</v>
       </c>
       <c r="I7" t="n">
-        <v>11.85896762513558</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="J7" t="n">
-        <v>1.668885927770414</v>
+        <v>1.744576111630545</v>
       </c>
       <c r="K7" t="n">
-        <v>11.85896762513558</v>
+        <v>12.02681808690701</v>
       </c>
     </row>
     <row r="8">
@@ -716,7 +716,7 @@
         <v>47849</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668885927770414</v>
+        <v>1.764862770177136</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -727,25 +727,25 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>38.83232050396268</v>
+        <v>16.55360533516066</v>
       </c>
       <c r="F8" t="n">
-        <v>1.668885927770414</v>
+        <v>1.764862770177137</v>
       </c>
       <c r="G8" t="n">
-        <v>38.83232050396268</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="H8" t="n">
-        <v>1.668885927770413</v>
+        <v>1.764862770177136</v>
       </c>
       <c r="I8" t="n">
-        <v>16.32257745401947</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="J8" t="n">
-        <v>1.668885927770414</v>
+        <v>1.764862770177137</v>
       </c>
       <c r="K8" t="n">
-        <v>16.32257745401947</v>
+        <v>16.55360533516066</v>
       </c>
     </row>
     <row r="9">
@@ -753,7 +753,7 @@
         <v>49675</v>
       </c>
       <c r="B9" t="n">
-        <v>1.72203695031119</v>
+        <v>1.781337669389687</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -764,25 +764,25 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>38.83232050396268</v>
+        <v>18.8204631381465</v>
       </c>
       <c r="F9" t="n">
-        <v>1.723041410039284</v>
+        <v>1.781088598481704</v>
       </c>
       <c r="G9" t="n">
-        <v>38.83232050396268</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="H9" t="n">
-        <v>1.72203695031119</v>
+        <v>1.781337669389687</v>
       </c>
       <c r="I9" t="n">
-        <v>18.55779820003381</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="J9" t="n">
-        <v>1.723041410039284</v>
+        <v>1.781088598481703</v>
       </c>
       <c r="K9" t="n">
-        <v>18.55779820003381</v>
+        <v>18.8204631381465</v>
       </c>
     </row>
     <row r="10">
@@ -790,7 +790,7 @@
         <v>51502</v>
       </c>
       <c r="B10" t="n">
-        <v>1.780896937953275</v>
+        <v>1.803614190664855</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -801,25 +801,25 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>38.83232050396268</v>
+        <v>20.15059880314304</v>
       </c>
       <c r="F10" t="n">
-        <v>1.781102472681083</v>
+        <v>1.803614190664857</v>
       </c>
       <c r="G10" t="n">
-        <v>38.83232050396268</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="H10" t="n">
-        <v>1.780896937953274</v>
+        <v>1.803614190664855</v>
       </c>
       <c r="I10" t="n">
-        <v>19.86937002844656</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="J10" t="n">
-        <v>1.781102472681083</v>
+        <v>1.803614190664857</v>
       </c>
       <c r="K10" t="n">
-        <v>19.86937002844656</v>
+        <v>20.15059880314304</v>
       </c>
     </row>
     <row r="11">
@@ -827,7 +827,7 @@
         <v>53328</v>
       </c>
       <c r="B11" t="n">
-        <v>1.783030930674917</v>
+        <v>1.785025082779787</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -838,25 +838,25 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>38.83232050396268</v>
+        <v>21.01808582652089</v>
       </c>
       <c r="F11" t="n">
-        <v>1.783030930674916</v>
+        <v>1.785025082779787</v>
       </c>
       <c r="G11" t="n">
-        <v>38.83232050396268</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="H11" t="n">
-        <v>1.783030930674915</v>
+        <v>1.785025082779787</v>
       </c>
       <c r="I11" t="n">
-        <v>20.72475010080856</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="J11" t="n">
-        <v>1.783030930674915</v>
+        <v>1.785025082779787</v>
       </c>
       <c r="K11" t="n">
-        <v>20.72475010080856</v>
+        <v>21.01808582652089</v>
       </c>
     </row>
     <row r="12">
@@ -875,7 +875,7 @@
         <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0.0867453946648023</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -887,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0867453946648023</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -912,7 +912,7 @@
         <v>100</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0.1343372936492743</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1343372936492743</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>100</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0.1647522628953677</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1647522628953677</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
         <v>100</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.1862401701876625</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -998,7 +998,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1862401701876625</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1023,7 +1023,7 @@
         <v>100</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0.202571092960545</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0.202571092960545</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1049,7 +1049,7 @@
         <v>46023</v>
       </c>
       <c r="B17" t="n">
-        <v>0.06987360984846264</v>
+        <v>0.07333373253921144</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1060,25 +1060,25 @@
         <v>175</v>
       </c>
       <c r="E17" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="F17" t="n">
-        <v>0.06987360984846264</v>
+        <v>0.07333373253921149</v>
       </c>
       <c r="G17" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="H17" t="n">
-        <v>0.06987360984846257</v>
+        <v>0.07333373253921144</v>
       </c>
       <c r="I17" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="J17" t="n">
-        <v>0.06987360984846264</v>
+        <v>0.07333373253921147</v>
       </c>
       <c r="K17" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
     </row>
     <row r="18">
@@ -1086,7 +1086,7 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.06987360984846264</v>
+        <v>0.07426112264419851</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1097,25 +1097,25 @@
         <v>175</v>
       </c>
       <c r="E18" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="F18" t="n">
-        <v>0.06987360984846264</v>
+        <v>0.07426112264419851</v>
       </c>
       <c r="G18" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="H18" t="n">
-        <v>0.06987360984846258</v>
+        <v>0.07426112264419849</v>
       </c>
       <c r="I18" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="J18" t="n">
-        <v>0.06987360984846264</v>
+        <v>0.07426112264419851</v>
       </c>
       <c r="K18" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
     </row>
     <row r="19">
@@ -1123,7 +1123,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.07230337087889811</v>
+        <v>0.07501426089391512</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1134,25 +1134,25 @@
         <v>175</v>
       </c>
       <c r="E19" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="F19" t="n">
-        <v>0.07234928903789667</v>
+        <v>0.07500287479526445</v>
       </c>
       <c r="G19" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="H19" t="n">
-        <v>0.07230337087889811</v>
+        <v>0.07501426089391512</v>
       </c>
       <c r="I19" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="J19" t="n">
-        <v>0.07234928903789668</v>
+        <v>0.07500287479526441</v>
       </c>
       <c r="K19" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
     </row>
     <row r="20">
@@ -1160,7 +1160,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.07499411317110753</v>
+        <v>0.07775327686857787</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1171,25 +1171,25 @@
         <v>175</v>
       </c>
       <c r="E20" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="F20" t="n">
-        <v>0.07500350904437884</v>
+        <v>0.07768388210098112</v>
       </c>
       <c r="G20" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="H20" t="n">
-        <v>0.07499411317110766</v>
+        <v>0.07775327686857789</v>
       </c>
       <c r="I20" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="J20" t="n">
-        <v>0.07500350904437879</v>
+        <v>0.07768388210098112</v>
       </c>
       <c r="K20" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
     </row>
     <row r="21">
@@ -1197,7 +1197,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.07509166712409703</v>
+        <v>0.07860306465760961</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1208,25 +1208,25 @@
         <v>175</v>
       </c>
       <c r="E21" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="F21" t="n">
-        <v>0.075091667124097</v>
+        <v>0.07853366989001288</v>
       </c>
       <c r="G21" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="H21" t="n">
-        <v>0.07509166712409697</v>
+        <v>0.07860306465760961</v>
       </c>
       <c r="I21" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="J21" t="n">
-        <v>0.07509166712409697</v>
+        <v>0.0785336698900129</v>
       </c>
       <c r="K21" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
     </row>
     <row r="22">
@@ -1245,7 +1245,7 @@
         <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>5.878502256181318</v>
+        <v>0.47079117807104</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1257,7 +1257,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0.47079117807104</v>
+        <v>5.878502256181318</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>5.878502256181318</v>
+        <v>0.742930397094833</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1294,7 +1294,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0.742930397094833</v>
+        <v>5.878502256181318</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
         <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>5.878502256181318</v>
+        <v>0.9247372801783194</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1331,7 +1331,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9247372801783194</v>
+        <v>5.878502256181318</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1356,7 +1356,7 @@
         <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>5.878502256181318</v>
+        <v>1.058489268339244</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1368,7 +1368,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>1.058489268339244</v>
+        <v>5.878502256181318</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>5.878502256181318</v>
+        <v>1.163707434539444</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1405,7 +1405,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1.163707434539444</v>
+        <v>5.878502256181318</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1430,7 +1430,7 @@
         <v>4.15</v>
       </c>
       <c r="E27" t="n">
-        <v>11.33205254203628</v>
+        <v>0.9075492589321255</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9075492589321255</v>
+        <v>11.33205254203628</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1467,7 +1467,7 @@
         <v>4.15</v>
       </c>
       <c r="E28" t="n">
-        <v>11.33205254203628</v>
+        <v>1.432154982351485</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1479,7 +1479,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>1.432154982351485</v>
+        <v>11.33205254203628</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1504,7 +1504,7 @@
         <v>4.15</v>
       </c>
       <c r="E29" t="n">
-        <v>11.33205254203628</v>
+        <v>1.782626082271459</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -1516,7 +1516,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1.782626082271459</v>
+        <v>11.33205254203628</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>4.15</v>
       </c>
       <c r="E30" t="n">
-        <v>11.33205254203628</v>
+        <v>2.040461240172037</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>2.040461240172037</v>
+        <v>11.33205254203628</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1578,7 +1578,7 @@
         <v>4.15</v>
       </c>
       <c r="E31" t="n">
-        <v>11.33205254203628</v>
+        <v>2.243291440076036</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1590,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>2.243291440076036</v>
+        <v>11.33205254203628</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1615,7 +1615,7 @@
         <v>300</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1567600601648352</v>
+        <v>0.01255443141522774</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0.01255443141522774</v>
+        <v>0.1567600601648352</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1652,7 +1652,7 @@
         <v>300</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1567600601648352</v>
+        <v>0.01981147725586221</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -1664,7 +1664,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0.01981147725586221</v>
+        <v>0.1567600601648352</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1689,7 +1689,7 @@
         <v>300</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1567600601648352</v>
+        <v>0.02465966080475518</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -1701,7 +1701,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>0.02465966080475518</v>
+        <v>0.1567600601648352</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
         <v>300</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1567600601648352</v>
+        <v>0.02822638048904651</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>0.02822638048904651</v>
+        <v>0.1567600601648352</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -1763,7 +1763,7 @@
         <v>300</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1567600601648352</v>
+        <v>0.03103219825438517</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0.03103219825438517</v>
+        <v>0.1567600601648352</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1783,151 +1783,6 @@
       <c r="K36" t="n">
         <v>0.03103219825438517</v>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>RE_GPV_s_1 MW_d_Ascona</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.1191671853885055</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.1191671853885055</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B38" t="n">
-        <v>0.1191671853885055</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>RE_GPV_s_1 MW_d_Ascona</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.1191671853885055</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.1191671853885055</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.1191671853885055</v>
-      </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B39" t="n">
-        <v>0.1191671853885055</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>RE_GPV_s_1 MW_d_Ascona</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.1191671853885055</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.1191671853885055</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.1191671853885055</v>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B40" t="n">
-        <v>0.1191671853885055</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>RE_GPV_s_1 MW_d_Ascona</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.1191671853885055</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.1191671853885055</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.1191671853885055</v>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B41" t="n">
-        <v>0.1191671853885055</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>RE_GPV_s_1 MW_d_Ascona</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0.1191671853885055</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.1191671853885055</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0.1191671853885055</v>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
